--- a/output/pdf_financials_xlsx/CLTE.xlsx
+++ b/output/pdf_financials_xlsx/CLTE.xlsx
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.014909</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.031606</v>
       </c>
     </row>
     <row r="35">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.014909</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.031606</v>
       </c>
     </row>
     <row r="37">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/CLTE.xlsx
+++ b/output/pdf_financials_xlsx/CLTE.xlsx
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="70">
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="72">
@@ -1567,10 +1567,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.01669353862676169</v>
       </c>
     </row>
     <row r="81">
@@ -1675,10 +1673,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.352595</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>3.053595</v>
       </c>
     </row>
     <row r="89">
@@ -2542,7 +2540,11 @@
           <t>Loan Payable Note 5</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -2568,7 +2570,11 @@
           <t>Due to related party Note 11</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.0018</v>
       </c>
@@ -2646,7 +2652,11 @@
           <t>Share capital Note 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.352595</v>
       </c>
@@ -3356,7 +3366,11 @@
           <t>Amortization Note 10 39,000</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>0.039</v>
       </c>

--- a/output/pdf_financials_xlsx/CLTE.xlsx
+++ b/output/pdf_financials_xlsx/CLTE.xlsx
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.000673</v>
+        <v>0.012673</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
@@ -3426,7 +3426,11 @@
           <t>Director fees 13,053</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.012</v>
       </c>
